--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdelrhman.gamal\Downloads\222\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D818FF24-87B0-46C3-9FBB-A7547DDECB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031A6121-37D8-47AB-B3A6-82DCE96D55DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="341">
   <si>
     <t>SAAFAH Dashboard Google Sheets Template</t>
   </si>
@@ -711,9 +711,6 @@
     <t>NADEC</t>
   </si>
   <si>
-    <t>Current dashboard item</t>
-  </si>
-  <si>
     <t>Feb</t>
   </si>
   <si>
@@ -819,18 +816,6 @@
     <t>Jan 2026</t>
   </si>
   <si>
-    <t>Imported from dashboard</t>
-  </si>
-  <si>
-    <t>SIDF</t>
-  </si>
-  <si>
-    <t>ESG Workshop</t>
-  </si>
-  <si>
-    <t>Sep 2025</t>
-  </si>
-  <si>
     <t>KSA Sustainability Champions</t>
   </si>
   <si>
@@ -840,18 +825,6 @@
     <t>Tadawul Group</t>
   </si>
   <si>
-    <t>GDP ESG Workshop</t>
-  </si>
-  <si>
-    <t>Oct 2025</t>
-  </si>
-  <si>
-    <t>Center For Gov.</t>
-  </si>
-  <si>
-    <t>ESG Course Development</t>
-  </si>
-  <si>
     <t>Won</t>
   </si>
   <si>
@@ -864,30 +837,6 @@
     <t>Feb 2026</t>
   </si>
   <si>
-    <t>ESG &amp; Corp. Governance</t>
-  </si>
-  <si>
-    <t>Aug 2025</t>
-  </si>
-  <si>
-    <t>KACST</t>
-  </si>
-  <si>
-    <t>Elevating KACST's ESG Story</t>
-  </si>
-  <si>
-    <t>KAUST</t>
-  </si>
-  <si>
-    <t>From Lab to Kingdom</t>
-  </si>
-  <si>
-    <t>King Saud Univ.</t>
-  </si>
-  <si>
-    <t>Future Proofing KSU Graduates</t>
-  </si>
-  <si>
     <t>Middle Beast</t>
   </si>
   <si>
@@ -915,15 +864,6 @@
     <t>ITQAN</t>
   </si>
   <si>
-    <t>Obeikan</t>
-  </si>
-  <si>
-    <t>RPI ESG Workshop</t>
-  </si>
-  <si>
-    <t>Nov 2025</t>
-  </si>
-  <si>
     <t>Tadawul ESG Course</t>
   </si>
   <si>
@@ -1092,33 +1032,9 @@
     <t>Owner</t>
   </si>
   <si>
-    <t>This Month</t>
-  </si>
-  <si>
-    <t>Active pipeline item</t>
-  </si>
-  <si>
-    <t>Auto-seeded from Pipeline_Revenue</t>
-  </si>
-  <si>
-    <t>Add lead rows here if you want the dashboard to show client-level detail for leads.</t>
-  </si>
-  <si>
     <t>This Week</t>
   </si>
   <si>
-    <t>Weekly detail is manual because the current raw opportunity source does not contain exact dates.</t>
-  </si>
-  <si>
-    <t>Add weekly active proposal detail here if needed.</t>
-  </si>
-  <si>
-    <t>Add weekly submitted detail here if needed.</t>
-  </si>
-  <si>
-    <t>Add weekly won detail here if needed.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nadec </t>
   </si>
   <si>
@@ -1147,6 +1063,9 @@
   </si>
   <si>
     <t>CFG</t>
+  </si>
+  <si>
+    <t>SAR 100,000</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1078,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1174,21 +1093,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1196,12 +1125,14 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1209,6 +1140,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1216,29 +1148,34 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1246,11 +1183,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1292,7 +1231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1331,112 +1270,129 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1516,7 +1472,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:I23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:I12">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Client"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Opportunity"/>
@@ -1750,24 +1706,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1800,12 +1756,12 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -2899,41 +2855,41 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3924,7 +3880,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3938,161 +3894,158 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>218</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="G4" s="30" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>343</v>
+      <c r="A5" s="33" t="s">
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
-      </c>
-      <c r="C5" t="s">
-        <v>228</v>
-      </c>
-      <c r="D5" t="s">
-        <v>350</v>
+        <v>329</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>223</v>
       </c>
       <c r="E5" s="32">
-        <v>330000</v>
-      </c>
-      <c r="G5" t="s">
-        <v>351</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
-        <v>342</v>
+      <c r="A6" s="33" t="s">
+        <v>322</v>
       </c>
       <c r="B6" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>224</v>
+        <v>330</v>
       </c>
       <c r="E6" s="32">
         <v>500000</v>
       </c>
-      <c r="G6" t="s">
-        <v>352</v>
-      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
-        <v>342</v>
+      <c r="A7" t="s">
+        <v>322</v>
       </c>
       <c r="B7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>358</v>
+        <v>329</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="E7" s="32">
         <v>500000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
-      <c r="C8" s="31"/>
-      <c r="E8" s="32"/>
+      <c r="A8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B8" t="s">
+        <v>329</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="E8" s="32">
+        <v>500000</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="B9" t="s">
-        <v>353</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>366</v>
+        <v>329</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>332</v>
       </c>
       <c r="E9" s="32">
-        <v>500000</v>
-      </c>
-      <c r="G9" t="s">
-        <v>354</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="B10" t="s">
-        <v>353</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>359</v>
+        <v>329</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>333</v>
       </c>
       <c r="E10" s="32">
-        <v>500000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="B11" t="s">
-        <v>353</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>360</v>
+        <v>329</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>334</v>
       </c>
       <c r="E11" s="32">
-        <v>700000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="B12" t="s">
-        <v>353</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>361</v>
+        <v>329</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>335</v>
       </c>
       <c r="E12" s="32">
-        <v>200000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="B13" t="s">
-        <v>353</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>362</v>
+        <v>329</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>336</v>
       </c>
       <c r="E13" s="32">
         <v>100000</v>
@@ -4100,158 +4053,139 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="B14" t="s">
-        <v>353</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>363</v>
+        <v>329</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>337</v>
       </c>
       <c r="E14" s="32">
-        <v>100000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="B15" t="s">
-        <v>353</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>364</v>
+        <v>329</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>223</v>
       </c>
       <c r="E15" s="32">
-        <v>100000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="B16" t="s">
-        <v>353</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>365</v>
+        <v>329</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>272</v>
       </c>
       <c r="E16" s="32">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>338</v>
+      </c>
+      <c r="E17" s="32">
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C17" s="38"/>
-      <c r="E17" s="32"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="B18" t="s">
-        <v>353</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>224</v>
+        <v>329</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>332</v>
       </c>
       <c r="E18" s="32">
-        <v>500000</v>
-      </c>
-      <c r="G18" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="B19" t="s">
-        <v>353</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>289</v>
+        <v>329</v>
+      </c>
+      <c r="C19" t="s">
+        <v>339</v>
       </c>
       <c r="E19" s="32">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="B20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>366</v>
+        <v>329</v>
+      </c>
+      <c r="C20" t="s">
+        <v>223</v>
       </c>
       <c r="E20" s="32">
         <v>500000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s">
-        <v>353</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>360</v>
-      </c>
-      <c r="E21" s="32">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C22" s="39"/>
-      <c r="E22" s="32"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>249</v>
+      </c>
+      <c r="B22" t="s">
+        <v>329</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s">
-        <v>353</v>
-      </c>
-      <c r="C23" t="s">
-        <v>367</v>
-      </c>
-      <c r="G23" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>250</v>
-      </c>
-      <c r="B24" t="s">
-        <v>353</v>
-      </c>
-      <c r="C24" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>250</v>
-      </c>
-      <c r="B25" t="s">
-        <v>349</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>269</v>
-      </c>
-      <c r="B26" t="s">
-        <v>353</v>
-      </c>
-      <c r="G26" t="s">
-        <v>357</v>
+        <v>329</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>339</v>
+      </c>
+      <c r="E23" s="42">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
@@ -4273,14 +4207,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -5700,32 +5634,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -5802,14 +5736,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -6971,32 +6905,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -7073,14 +7007,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -8324,32 +8258,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="34"/>
+      <c r="B3" s="39"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -8368,10 +8302,10 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="39"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -8437,11 +8371,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -8477,10 +8411,10 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="34"/>
+      <c r="B17" s="39"/>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -8532,10 +8466,10 @@
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="B25" s="34"/>
+      <c r="B25" s="39"/>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -9577,35 +9511,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -9653,13 +9587,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -9710,13 +9644,11 @@
       <c r="H11" s="22">
         <v>500000</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B12" s="13">
         <v>0</v>
@@ -9732,18 +9664,16 @@
         <v>128</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H12" s="22">
         <v>500000</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B13" s="13">
         <v>0</v>
@@ -9759,18 +9689,16 @@
         <v>128</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H13" s="22">
         <v>350000</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B14" s="13">
         <v>0</v>
@@ -9786,18 +9714,16 @@
         <v>129</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H14" s="22">
         <v>330000</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B15" s="13">
         <v>100000</v>
@@ -9813,18 +9739,16 @@
         <v>129</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H15" s="22">
         <v>220000</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B16" s="13">
         <v>185000</v>
@@ -9840,18 +9764,16 @@
         <v>129</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H16" s="22">
         <v>70000</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B17" s="13">
         <v>136125</v>
@@ -9867,18 +9789,16 @@
         <v>130</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H17" s="22">
         <v>50000</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B18" s="13">
         <v>170156</v>
@@ -9894,18 +9814,16 @@
         <v>130</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H18" s="22">
         <v>45000</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B19" s="13">
         <v>331064</v>
@@ -9921,18 +9839,16 @@
         <v>130</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H19" s="22">
         <v>30000</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B20" s="13">
         <v>276963</v>
@@ -9948,7 +9864,7 @@
         <v>131</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H20" s="21">
         <f>SUM(H11:H19)</f>
@@ -9957,7 +9873,7 @@
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B21" s="13">
         <v>330051</v>
@@ -9975,7 +9891,7 @@
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B22" s="13">
         <v>299067</v>
@@ -9993,7 +9909,7 @@
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B23" s="14">
         <f>SUM(B11:B22)</f>
@@ -10011,14 +9927,14 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
+      <c r="A25" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
@@ -10092,7 +10008,7 @@
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B29" s="14">
         <f>B27+B28</f>
@@ -11101,7 +11017,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I1001"/>
+  <dimension ref="A1:I990"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -11116,53 +11032,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+    </row>
+    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="38" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>38</v>
@@ -11170,16 +11086,16 @@
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>256</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>257</v>
       </c>
       <c r="E4" s="13">
         <v>30000</v>
@@ -11188,73 +11104,69 @@
         <v>0.95</v>
       </c>
       <c r="G4" s="14">
-        <f t="shared" ref="G4:G10" si="0">IF(AND(E4&lt;&gt;0,NOT(ISBLANK(E4)),NOT(ISBLANK(F4))),E4*F4,"")</f>
+        <f t="shared" ref="G4:G6" si="0">IF(AND(E4&lt;&gt;0,NOT(ISBLANK(E4)),NOT(ISBLANK(F4))),E4*F4,"")</f>
         <v>28500</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>258</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E5" s="13">
-        <v>75000</v>
+        <v>500000</v>
       </c>
       <c r="F5" s="23">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="G5" s="14">
         <f t="shared" si="0"/>
-        <v>75000</v>
+        <v>425000</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>258</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>262</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="E6" s="13"/>
+      <c r="E6" s="13">
+        <v>500000</v>
+      </c>
       <c r="F6" s="23">
-        <v>0.85</v>
-      </c>
-      <c r="G6" s="14" t="str">
+        <v>0.6</v>
+      </c>
+      <c r="G6" s="14">
         <f t="shared" si="0"/>
-        <v/>
+        <v>300000</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>258</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="I6" s="12"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
@@ -11264,506 +11176,186 @@
         <v>265</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>266</v>
       </c>
       <c r="E7" s="13">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="F7" s="23">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="14">
-        <f t="shared" si="0"/>
-        <v>400000</v>
+        <f t="shared" ref="G7:G12" si="1">IF(AND(E7&lt;&gt;0,NOT(ISBLANK(E7)),NOT(ISBLANK(F7))),E7*F7,"")</f>
+        <v>50000</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>258</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="I7" s="12"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>256</v>
-      </c>
       <c r="D8" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E8" s="13">
-        <v>20000</v>
+        <v>500000</v>
       </c>
       <c r="F8" s="23">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G8" s="14">
-        <f t="shared" si="0"/>
-        <v>20000</v>
+        <f t="shared" si="1"/>
+        <v>250000</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>258</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="I8" s="12"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>272</v>
-      </c>
       <c r="E9" s="13">
-        <v>500000</v>
+        <v>90000</v>
       </c>
       <c r="F9" s="23">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="14">
-        <f t="shared" si="0"/>
-        <v>300000</v>
+        <f t="shared" si="1"/>
+        <v>45000</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>258</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="E10" s="13">
+        <v>100000</v>
+      </c>
+      <c r="F10" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="14">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="E10" s="13">
-        <v>1000000</v>
-      </c>
-      <c r="F10" s="23">
-        <v>0.6</v>
-      </c>
-      <c r="G10" s="14">
-        <f t="shared" si="0"/>
-        <v>600000</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>276</v>
-      </c>
       <c r="C11" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="E11" s="13"/>
+        <v>263</v>
+      </c>
+      <c r="E11" s="13">
+        <v>30000</v>
+      </c>
       <c r="F11" s="23">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G11" s="14">
-        <v>50000</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G12" s="14">
-        <v>50000</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G13" s="14">
-        <v>50000</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="E14" s="13">
-        <v>100000</v>
-      </c>
-      <c r="F14" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G14" s="14">
-        <f t="shared" ref="G14:G23" si="1">IF(AND(E14&lt;&gt;0,NOT(ISBLANK(E14)),NOT(ISBLANK(F14))),E14*F14,"")</f>
-        <v>50000</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="E15" s="13">
-        <v>500000</v>
-      </c>
-      <c r="F15" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="14">
-        <f t="shared" si="1"/>
-        <v>250000</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="E16" s="13">
-        <v>90000</v>
-      </c>
-      <c r="F16" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="14">
-        <f t="shared" si="1"/>
-        <v>45000</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="E18" s="13">
-        <v>195000</v>
-      </c>
-      <c r="F18" s="23">
-        <v>0.4</v>
-      </c>
-      <c r="G18" s="14">
-        <f t="shared" si="1"/>
-        <v>78000</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="E19" s="13">
-        <v>100000</v>
-      </c>
-      <c r="F19" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="14">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
-      <c r="H19" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I19" s="12" t="s">
+      <c r="H11" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="E20" s="13">
-        <v>45000</v>
-      </c>
-      <c r="F20" s="23">
-        <v>0.6</v>
-      </c>
-      <c r="G20" s="14">
-        <f t="shared" si="1"/>
-        <v>27000</v>
-      </c>
-      <c r="H20" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="E21" s="13">
-        <v>30000</v>
-      </c>
-      <c r="F21" s="23">
-        <v>1</v>
-      </c>
-      <c r="G21" s="14">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="E22" s="13">
-        <v>140000</v>
-      </c>
-      <c r="F22" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G22" s="14">
-        <f t="shared" si="1"/>
-        <v>70000</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="E23" s="13">
+      <c r="E12" s="13">
         <v>100000</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F12" s="23">
         <v>0</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G12" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H23" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="H12" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -12722,17 +12314,6 @@
     <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
@@ -12757,42 +12338,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="A1" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="A2" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="C4" s="23">
         <v>1</v>
@@ -12800,10 +12381,10 @@
     </row>
     <row r="5" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="C5" s="23">
         <v>1</v>
@@ -12811,10 +12392,10 @@
     </row>
     <row r="6" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="C6" s="23">
         <v>0.5</v>
@@ -12822,10 +12403,10 @@
     </row>
     <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="C7" s="23">
         <v>0.5</v>
@@ -12833,10 +12414,10 @@
     </row>
     <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="C8" s="23">
         <v>0.5</v>
@@ -12844,10 +12425,10 @@
     </row>
     <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="C9" s="23">
         <v>0.4</v>
@@ -12855,10 +12436,10 @@
     </row>
     <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="C10" s="23">
         <v>0.3</v>
@@ -12866,10 +12447,10 @@
     </row>
     <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="C11" s="23">
         <v>0.3</v>
@@ -12877,10 +12458,10 @@
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="C12" s="23">
         <v>0.3</v>
@@ -12888,10 +12469,10 @@
     </row>
     <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="C13" s="23">
         <v>0.2</v>
@@ -13907,64 +13488,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>315</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="A2" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
-        <v>316</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="A3" s="41" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>116</v>
@@ -13972,7 +13553,7 @@
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="B5" s="13">
         <v>9</v>
@@ -13984,7 +13565,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="F5" s="13">
         <v>7</v>
@@ -13997,7 +13578,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -14013,8 +13594,7 @@
         <v>2095000</v>
       </c>
       <c r="D6" s="13">
-        <f>COUNTIF(Pipeline_Revenue!A11:A19,"Apr")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="13">
@@ -14025,29 +13605,30 @@
       </c>
       <c r="H6" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G6)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Submitted")</f>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C7" s="13">
         <f>SUMIF(Sales_Raw_Opportunities!H:H,"Submitted",Sales_Raw_Opportunities!E:E)</f>
-        <v>3275000</v>
+        <v>1820000</v>
       </c>
       <c r="D7" s="13">
-        <f>COUNTIFS(Sales_Raw_Opportunities!H:H,"Submitted",Sales_Raw_Opportunities!D:D,"Apr 2026")</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="24"/>
+        <v>1</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>340</v>
+      </c>
       <c r="F7" s="13">
         <v>2</v>
       </c>
@@ -14056,23 +13637,23 @@
       </c>
       <c r="H7" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G7)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="B8" s="13">
         <f>COUNTIF(Sales_Raw_Opportunities!H:H,"Won")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="13">
         <f>SUMIF(Sales_Raw_Opportunities!H:H,"Won",Sales_Raw_Opportunities!E:E)</f>
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="D8" s="13">
         <f>COUNTIFS(Sales_Raw_Opportunities!H:H,"Won",Sales_Raw_Opportunities!D:D,"Apr 2026")</f>
@@ -14087,43 +13668,43 @@
       </c>
       <c r="H8" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G8)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
       <c r="G9" s="26">
         <v>0.6</v>
       </c>
       <c r="H9" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G9)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>206</v>
@@ -14136,12 +13717,12 @@
         <v>0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="B11" s="14">
         <f t="shared" ref="B11:C14" si="0">B5</f>
@@ -14155,22 +13736,22 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="G11" s="26">
         <v>0.8</v>
       </c>
       <c r="H11" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G11)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="B12" s="14">
         <f t="shared" si="0"/>
@@ -14185,7 +13766,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="G12" s="26">
         <v>0.85</v>
@@ -14195,24 +13776,24 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="B13" s="14">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C13" s="14">
         <f t="shared" si="0"/>
-        <v>3275000</v>
+        <v>1820000</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="G13" s="26">
         <v>0.95</v>
@@ -14222,59 +13803,59 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="B14" s="14">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="14">
         <f t="shared" si="0"/>
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="D14" s="15">
         <f>IFERROR(B14/B13,0)</f>
-        <v>0.11764705882352941</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="G14" s="26">
         <v>1</v>
       </c>
       <c r="H14" s="21">
         <f>COUNTIF(Sales_Raw_Opportunities!F:F,G14)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
-        <v>335</v>
-      </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
+      <c r="A15" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="B16" s="34"/>
+      <c r="A16" s="41" t="s">
+        <v>316</v>
+      </c>
+      <c r="B16" s="39"/>
       <c r="G16" s="18" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>218</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -14282,17 +13863,15 @@
         <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="27" t="s">
-        <v>264</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H17" s="27"/>
       <c r="I17" s="21">
         <f>SUMIF(Sales_Raw_Opportunities!A:A,H17,Sales_Raw_Opportunities!E:E)</f>
-        <v>1590000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -14341,12 +13920,12 @@
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
